--- a/data/horizon_cadence_transformed.xlsx
+++ b/data/horizon_cadence_transformed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,1090 +417,1048 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>isNew</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>quadrant</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>ring</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>quadrant</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>isNew</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>customer</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>value</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>owner</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Swisscom-OIZ-Bedag</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Valentine Sprint&lt;/strong&gt; — Team: Swisscom-OIZ-Bedag. Brand: Cross.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Valentine Sprint</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>on-track</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Valentine Sprint&lt;/strong&gt; — Team: Swisscom-OIZ-Bedag. Brand: Cross.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Swisscom-OIZ-Bedag</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Roger Staubli (Head of Appl. Ops)&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Swisscom Due: 2026-02-19&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Valentine Sprint - Roger Staubli (Head of Appl. Ops)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Roger Staubli (Head of Appl. Ops)&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Swisscom Due: 2026-02-19&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Urs Lehner Rüschlikon&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Swisscom Due: 2026-02-18 Urs Kübli&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Valentine Sprint - Urs Lehner Rüschlikon</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Urs Lehner Rüschlikon&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Swisscom Due: 2026-02-18 Urs Kübli&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Lukas Hebeisen asap&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Swisscom über Frank&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Valentine Sprint - Lukas Hebeisen asap</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Lukas Hebeisen asap&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Swisscom über Frank&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Stadt ZH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Retho Hirt&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Stadt ZH Due: 2026-02-13 Lunch with Lead Architekt&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Valentine Sprint - Retho Hirt</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>jtho@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Retho Hirt&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Stadt ZH Due: 2026-02-13 Lunch with Lead Architekt&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Stadt ZH</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>jtho@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Bedag</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Werner Stocker to get into Bedag and OIZ&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Bedag&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Valentine Sprint - Werner Stocker to get into Bedag and OIZ</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Werner Stocker to get into Bedag and OIZ&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Bedag&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Bedag</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Stadt ZH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Andreas Nemeth&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Stadt ZH Oliver geht auf Angelo Gisoldo von RH zu, Markus Danhel prüft Ruechlikon agenda&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Valentine Sprint - Andreas Nemeth</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Andreas Nemeth&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Stadt ZH Oliver geht auf Angelo Gisoldo von RH zu, Markus Danhel prüft Ruechlikon agenda&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Stadt ZH</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Stadt ZH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Hermann Huber&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Stadt ZH Due: 2026-03-24 24.03. Meeting mit OIZ mit Jörg&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Valentine Sprint - Hermann Huber</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Hermann Huber&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Stadt ZH Due: 2026-03-24 24.03. Meeting mit OIZ mit Jörg&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Stadt ZH</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Swisscom&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Swisscom Due: 2026-02-18&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Valentine Sprint - Swisscom</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>jtho@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>on-track</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Swisscom&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Swisscom Due: 2026-02-18&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>bedag,cross,oiz,swisscom</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>jtho@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>['bedag', 'cross', 'oiz', 'swisscom']</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Stadt ZH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;OIZ&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Stadt ZH Due: 2026-03-12 Prepcall 12.2.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Valentine Sprint - OIZ</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jtho@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>on-track</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;OIZ&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Stadt ZH Due: 2026-03-12 Prepcall 12.2.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Stadt ZH</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>jtho@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Bedag</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Bedag&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Bedag Q4&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Valentine Sprint - Bedag</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>jtho@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Hold</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>at-risk</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Bedag&lt;/strong&gt; under &lt;em&gt;Valentine Sprint&lt;/em&gt;. Client: Bedag Q4&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Bedag</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>jtho@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Maximo Oppty&lt;/strong&gt; - Team: Swisscom-OIZ-Bedag. Brand: Automation.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Maximo Oppty</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Automation</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>automation</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>on-track</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Maximo Oppty&lt;/strong&gt; — Team: Swisscom-OIZ-Bedag. Brand: Automation.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>automation,bedag,oiz,swisscom</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>automation, bedag, oiz, swisscom</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;PoC frühestens im März&lt;/strong&gt; under &lt;em&gt;Maximo Oppty&lt;/em&gt;. Client: Swisscom Due: 2026-03-31&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Maximo Oppty - PoC frühestens im März</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Automation</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;PoC frühestens im März&lt;/strong&gt; under &lt;em&gt;Maximo Oppty&lt;/em&gt;. Client: Swisscom Due: 2026-03-31&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>automation,bedag,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;IWA Oppty&lt;/strong&gt; — Team: Swisscom-OIZ-Bedag. Brand: Automation.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>IWA Oppty</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Automation</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>on-track</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;IWA Oppty&lt;/strong&gt; — Team: Swisscom-OIZ-Bedag. Brand: Automation.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>automation,bedag,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;H2 deal, müssen mit dem Kunden timing besprechen&lt;/strong&gt; under &lt;em&gt;IWA Oppty&lt;/em&gt;. Client: Swisscom Kunde hat 1 Jahr mit Broadcom verlängert&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C16" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>IWA Oppty - H2 deal, müssen mit dem Kunden timing besprechen</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Automation</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;H2 deal, müssen mit dem Kunden timing besprechen&lt;/strong&gt; under &lt;em&gt;IWA Oppty&lt;/em&gt;. Client: Swisscom Kunde hat 1 Jahr mit Broadcom verlängert&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>automation,bedag,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;MQ Oppty&lt;/strong&gt; — Team: Swisscom-OIZ-Bedag. Brand: Automation.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>MQ Oppty</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Automation</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;MQ Oppty&lt;/strong&gt; — Team: Swisscom-OIZ-Bedag. Brand: Automation.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>automation,bedag,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Q2 pull foward&lt;/strong&gt; under &lt;em&gt;MQ Oppty&lt;/em&gt;. Client: Swisscom&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>MQ Oppty - Q2 pull foward</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Automation</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Q2 pull foward&lt;/strong&gt; under &lt;em&gt;MQ Oppty&lt;/em&gt;. Client: Swisscom&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>automation,bedag,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Sovereign Core&lt;/strong&gt; — Team: Swisscom-OIZ-Bedag. Brand: Cross.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C19" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Sovereign Core</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Sovereign Core&lt;/strong&gt; — Team: Swisscom-OIZ-Bedag. Brand: Cross.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Frank Meier&lt;/strong&gt; under &lt;em&gt;Sovereign Core&lt;/em&gt;. Client: Swisscom Due: 2026-02-13 Frank brieft Lukas Hebeisen, check progress if Frank does not react&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Sovereign Core - Frank Meier</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Frank Meier&lt;/strong&gt; under &lt;em&gt;Sovereign Core&lt;/em&gt;. Client: Swisscom Due: 2026-02-13 Frank brieft Lukas Hebeisen, check progress if Frank does not react&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;ELA / IFSA&lt;/strong&gt; — Team: Swisscom-OIZ-Bedag. Brand: Cross.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>ELA / IFSA</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;ELA / IFSA&lt;/strong&gt; — Team: Swisscom-OIZ-Bedag. Brand: Cross.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Swisscom</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Gather potential&lt;/strong&gt; under &lt;em&gt;ELA / IFSA&lt;/em&gt;. Client: Swisscom Get in touch with procurement through Mark Hoffmann&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C22" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>ELA / IFSA - Gather potential</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>OBET@ch.ibm.com</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Explore</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Gather potential&lt;/strong&gt; under &lt;em&gt;ELA / IFSA&lt;/em&gt;. Client: Swisscom Get in touch with procurement through Mark Hoffmann&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>bedag,cross,oiz,swisscom</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Swisscom</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>OBET@ch.ibm.com</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horizon_cadence_transformed.xlsx
+++ b/data/horizon_cadence_transformed.xlsx
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="C16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>automation</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>explore</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>automation,bedag,oiz,swisscom</t>
+          <t>automation, bedag, oiz, swisscom</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>

--- a/data/horizon_cadence_transformed.xlsx
+++ b/data/horizon_cadence_transformed.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>['bedag', 'cross', 'oiz', 'swisscom']</t>
+          <t>bedag, cross, oiz, swisscom</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
